--- a/data/trans_orig/P1425-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1425-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2007</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>7588</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265584</t>
+          <t>265422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272106</t>
+          <t>272117</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252461</t>
+          <t>252412</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259879</t>
+          <t>259874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>521078</t>
+          <t>521827</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531841</t>
+          <t>531664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,77 +1095,77 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1926</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11584</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>8272</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>3679</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>16500</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>1,65%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5288</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1908</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11897</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>8272</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>3957</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>15445</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>484931</t>
+          <t>484964</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492210</t>
+          <t>492207</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,82 +1203,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>498661</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>492365</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>502023</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>988752</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>980524</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>993345</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>98,35%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>498661</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>492052</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>502041</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>956</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>988752</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>981579</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>993067</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312348</t>
+          <t>311458</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330778</t>
+          <t>330737</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645971</t>
+          <t>646080</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>12661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20815</t>
+          <t>20343</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345072</t>
+          <t>346010</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356060</t>
+          <t>356142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>359565</t>
+          <t>360220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369559</t>
+          <t>369550</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>709312</t>
+          <t>709784</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>723706</t>
+          <t>723740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>9889</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>10372</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16072</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193510</t>
+          <t>193419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201557</t>
+          <t>201623</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198814</t>
+          <t>197296</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206545</t>
+          <t>206532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>394904</t>
+          <t>395363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>406923</t>
+          <t>407464</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265642</t>
+          <t>264897</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>272184</t>
+          <t>271808</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>541770</t>
+          <t>540825</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>602033</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>612219</t>
+          <t>612339</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>628709</t>
+          <t>628276</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>637302</t>
+          <t>637289</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1235226</t>
+          <t>1234973</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1247749</t>
+          <t>1247730</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23693</t>
+          <t>23617</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23806</t>
+          <t>22685</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>19019</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40840</t>
+          <t>41228</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>720102</t>
+          <t>720178</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>735837</t>
+          <t>735867</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>759705</t>
+          <t>760826</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>776484</t>
+          <t>776111</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1486466</t>
+          <t>1486078</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1508429</t>
+          <t>1508287</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>29694</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54004</t>
+          <t>54318</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,82 +3491,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>36848</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>24563</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>50002</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>77580</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>61383</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>97777</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>36848</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>26157</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>50834</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>77580</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>61588</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>95599</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3222539</t>
+          <t>3222225</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3246442</t>
+          <t>3246849</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,82 +3604,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3261</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3342349</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3329195</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3354634</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6434</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6578161</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6557964</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6594358</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3261</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>3342349</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>3328363</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3353040</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6434</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6578161</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6560142</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6594153</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2012</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287195</t>
+          <t>287266</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293848</t>
+          <t>293851</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280036</t>
+          <t>280738</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>571235</t>
+          <t>571508</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>580131</t>
+          <t>580171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>16451</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>16860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>487721</t>
+          <t>489076</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503513</t>
+          <t>503490</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>517644</t>
+          <t>517325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1012294</t>
+          <t>1012432</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1027111</t>
+          <t>1027146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16542</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>314134</t>
+          <t>313409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322215</t>
+          <t>322212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330425</t>
+          <t>331404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>339928</t>
+          <t>339925</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>648524</t>
+          <t>648748</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>660957</t>
+          <t>661036</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>368287</t>
+          <t>368184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>379051</t>
+          <t>378338</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>752173</t>
+          <t>751447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>761889</t>
+          <t>761897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,62 +5462,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1134</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6565</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1134</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5719</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>207034</t>
+          <t>205791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>217613</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>219591</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>426490</t>
+          <t>425644</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12729</t>
+          <t>13758</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265880</t>
+          <t>264862</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273034</t>
+          <t>273022</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269403</t>
+          <t>269355</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277042</t>
+          <t>277034</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>539348</t>
+          <t>538319</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549986</t>
+          <t>549902</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21301</t>
+          <t>19698</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>650047</t>
+          <t>649936</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>660743</t>
+          <t>660725</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>681810</t>
+          <t>682506</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>692077</t>
+          <t>692860</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1335340</t>
+          <t>1336943</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1351034</t>
+          <t>1351221</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21731</t>
+          <t>21556</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762711</t>
+          <t>762109</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776906</t>
+          <t>776924</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>812510</t>
+          <t>813618</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>821525</t>
+          <t>821521</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1579945</t>
+          <t>1580120</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1597266</t>
+          <t>1597123</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21978</t>
+          <t>22583</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47551</t>
+          <t>47346</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13340</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32525</t>
+          <t>34047</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>40640</t>
+          <t>39692</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>73422</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3379228</t>
+          <t>3379433</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3404801</t>
+          <t>3404196</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3522573</t>
+          <t>3521051</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3541758</t>
+          <t>3541752</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6908455</t>
+          <t>6910423</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6941237</t>
+          <t>6942185</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2016</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15650</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24661</t>
+          <t>22016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282037</t>
+          <t>281712</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291795</t>
+          <t>291974</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273053</t>
+          <t>272239</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>286580</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>557803</t>
+          <t>560448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>576273</t>
+          <t>576134</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -7721,97 +7721,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2153</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7643</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2153</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7328</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>7862</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2153</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>6703</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>500548</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>515756</t>
+          <t>515441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1018956</t>
+          <t>1017797</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,47 +8099,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8796</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>3197</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>976</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8987</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>3197</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>965</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316745</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318565</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327322</t>
+          <t>327513</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335333</t>
+          <t>335335</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645744</t>
+          <t>645488</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653909</t>
+          <t>653898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>8696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9677</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>361238</t>
+          <t>361268</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369071</t>
+          <t>369073</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>381381</t>
+          <t>382096</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>747570</t>
+          <t>748128</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>756262</t>
+          <t>756270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201035</t>
+          <t>199086</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210168</t>
+          <t>209240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>210197</t>
+          <t>210250</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217696</t>
+          <t>217701</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>414896</t>
+          <t>414628</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425897</t>
+          <t>425951</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9359</t>
+          <t>9495</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14443</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253764</t>
+          <t>253628</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262147</t>
+          <t>262157</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262359</t>
+          <t>264176</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272080</t>
+          <t>272081</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>521795</t>
+          <t>521911</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533129</t>
+          <t>533242</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>14895</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25239</t>
+          <t>26047</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>639947</t>
+          <t>641663</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>653426</t>
+          <t>653706</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>675048</t>
+          <t>674783</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688222</t>
+          <t>688423</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1322613</t>
+          <t>1321805</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1339393</t>
+          <t>1339622</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15625</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>13221</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23448</t>
+          <t>22725</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762958</t>
+          <t>764308</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775094</t>
+          <t>774911</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>812980</t>
+          <t>812946</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>823232</t>
+          <t>823483</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1581302</t>
+          <t>1582025</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1596206</t>
+          <t>1597295</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43640</t>
+          <t>45296</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23590</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47697</t>
+          <t>47721</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>50294</t>
+          <t>49228</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>83566</t>
+          <t>85810</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3350710</t>
+          <t>3349054</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3373070</t>
+          <t>3371866</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3496845</t>
+          <t>3496821</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3520952</t>
+          <t>3521891</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6855326</t>
+          <t>6853082</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6888598</t>
+          <t>6889664</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1425-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1425-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7588</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265422</t>
+          <t>265552</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272117</t>
+          <t>272119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252412</t>
+          <t>252660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259874</t>
+          <t>259863</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>521827</t>
+          <t>521531</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531664</t>
+          <t>531152</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16500</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>484964</t>
+          <t>484781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492207</t>
+          <t>492213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>492365</t>
+          <t>492373</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502023</t>
+          <t>501852</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>980524</t>
+          <t>980371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>993345</t>
+          <t>993006</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311458</t>
+          <t>310413</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330737</t>
+          <t>330789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646080</t>
+          <t>645206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653337</t>
+          <t>653333</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11236</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20343</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>346010</t>
+          <t>345856</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356142</t>
+          <t>356098</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>360220</t>
+          <t>360369</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369550</t>
+          <t>369558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>709784</t>
+          <t>709490</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>723740</t>
+          <t>723867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9889</t>
+          <t>10017</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10372</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193419</t>
+          <t>193291</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201623</t>
+          <t>201543</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197296</t>
+          <t>197601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206532</t>
+          <t>206534</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>395363</t>
+          <t>395452</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407464</t>
+          <t>406929</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264897</t>
+          <t>265692</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>271808</t>
+          <t>271641</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>540825</t>
+          <t>541127</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18273</t>
+          <t>17553</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602033</t>
+          <t>601935</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>612339</t>
+          <t>612232</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>628276</t>
+          <t>628331</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>637289</t>
+          <t>637285</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1234973</t>
+          <t>1235693</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1247730</t>
+          <t>1247666</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23617</t>
+          <t>24620</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22685</t>
+          <t>23418</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19019</t>
+          <t>18985</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41228</t>
+          <t>40594</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>720178</t>
+          <t>719175</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>735867</t>
+          <t>735943</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>760826</t>
+          <t>760093</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>776111</t>
+          <t>776159</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1486078</t>
+          <t>1486712</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1508287</t>
+          <t>1508321</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29694</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>53903</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24563</t>
+          <t>26169</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50002</t>
+          <t>51608</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>61383</t>
+          <t>62951</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>97777</t>
+          <t>96573</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3222225</t>
+          <t>3222640</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3246849</t>
+          <t>3247132</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3329195</t>
+          <t>3327589</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3354634</t>
+          <t>3353028</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6557964</t>
+          <t>6559168</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6594358</t>
+          <t>6592790</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>11894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287266</t>
+          <t>288149</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293851</t>
+          <t>293857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280738</t>
+          <t>279652</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>571508</t>
+          <t>570089</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>580171</t>
+          <t>580135</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16451</t>
+          <t>16214</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16860</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489076</t>
+          <t>489313</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503490</t>
+          <t>503516</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>517325</t>
+          <t>518199</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1012432</t>
+          <t>1012098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1027146</t>
+          <t>1027057</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16318</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313409</t>
+          <t>313326</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322212</t>
+          <t>322167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331404</t>
+          <t>330228</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>339925</t>
+          <t>339926</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>648748</t>
+          <t>648141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>661036</t>
+          <t>660741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>368184</t>
+          <t>368799</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>378338</t>
+          <t>380292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>751447</t>
+          <t>751631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>761897</t>
+          <t>761891</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205791</t>
+          <t>206895</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>425644</t>
+          <t>426937</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13758</t>
+          <t>12448</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264862</t>
+          <t>265745</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273022</t>
+          <t>273025</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269355</t>
+          <t>269546</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277034</t>
+          <t>277050</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538319</t>
+          <t>539629</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549902</t>
+          <t>549996</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19698</t>
+          <t>19009</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649936</t>
+          <t>650708</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>660725</t>
+          <t>660792</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>682506</t>
+          <t>681819</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>692860</t>
+          <t>692880</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1336943</t>
+          <t>1337632</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1351221</t>
+          <t>1350926</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>17319</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21556</t>
+          <t>21858</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762109</t>
+          <t>761779</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>776924</t>
+          <t>776029</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>813618</t>
+          <t>813596</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>821521</t>
+          <t>821524</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1580120</t>
+          <t>1579818</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1597123</t>
+          <t>1596315</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22583</t>
+          <t>22727</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47346</t>
+          <t>47552</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34047</t>
+          <t>33764</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39692</t>
+          <t>41518</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>71454</t>
+          <t>73379</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3379433</t>
+          <t>3379227</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3404196</t>
+          <t>3404052</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3521051</t>
+          <t>3521334</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3541752</t>
+          <t>3541640</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6910423</t>
+          <t>6908498</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6942185</t>
+          <t>6940359</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22016</t>
+          <t>22111</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281712</t>
+          <t>282575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291974</t>
+          <t>292174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272239</t>
+          <t>272148</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286580</t>
+          <t>286620</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>560448</t>
+          <t>560353</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>576134</t>
+          <t>576716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7273</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>515441</t>
+          <t>515295</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1017797</t>
+          <t>1018386</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>8785</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327513</t>
+          <t>327524</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335335</t>
+          <t>335336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645488</t>
+          <t>646079</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>361268</t>
+          <t>361052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369073</t>
+          <t>369074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>382096</t>
+          <t>382125</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>748128</t>
+          <t>748260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12135</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199086</t>
+          <t>200102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209240</t>
+          <t>209266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>210250</t>
+          <t>209237</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217701</t>
+          <t>217698</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>414628</t>
+          <t>415016</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425951</t>
+          <t>426174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>9635</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>14279</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253628</t>
+          <t>253488</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262157</t>
+          <t>262171</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>264176</t>
+          <t>263856</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272081</t>
+          <t>272084</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>521911</t>
+          <t>521959</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533242</t>
+          <t>533315</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14895</t>
+          <t>15761</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>15519</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26047</t>
+          <t>25948</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>641663</t>
+          <t>640797</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>653706</t>
+          <t>654318</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>674783</t>
+          <t>675775</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688423</t>
+          <t>688070</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1321805</t>
+          <t>1321904</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1339622</t>
+          <t>1339791</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>22587</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764308</t>
+          <t>763920</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774911</t>
+          <t>775283</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>812946</t>
+          <t>813055</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>823483</t>
+          <t>824023</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1582025</t>
+          <t>1582163</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1597295</t>
+          <t>1596765</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45296</t>
+          <t>45168</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22651</t>
+          <t>23612</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47721</t>
+          <t>47907</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49228</t>
+          <t>48836</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>85810</t>
+          <t>82304</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3349054</t>
+          <t>3349182</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3371866</t>
+          <t>3372394</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3496821</t>
+          <t>3496635</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3521891</t>
+          <t>3520930</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6853082</t>
+          <t>6856588</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6889664</t>
+          <t>6890056</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
